--- a/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92535424551</v>
+        <v>46157.93108480087</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108480087</v>
+        <v>46157.93364701494</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93364701494</v>
+        <v>46157.93665517443</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93665517443</v>
+        <v>46158.28191306016</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28191306016</v>
+        <v>46158.29709523988</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29709523988</v>
+        <v>46158.29785678902</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29785678902</v>
+        <v>46158.33352362308</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33352362308</v>
+        <v>46158.37208836128</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.3_Определения_и_акты_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37208836128</v>
+        <v>46158.37425147985</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
